--- a/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260715.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260715.xlsx
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2606</t>
+          <t>9910</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>裕民</t>
+          <t>豐泰</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>38,623,000</t>
+          <t>36,740,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>9910</t>
+          <t>9941</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>豐泰</t>
+          <t>裕融</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>36,740,000</t>
+          <t>29,940,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>9941</t>
+          <t>2606</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>裕融</t>
+          <t>裕民</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>29,940,000</t>
+          <t>38,623,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>6670</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>東陽</t>
+          <t>復盛應用</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>27,850,000</t>
+          <t>7,990,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>6670</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>復盛應用</t>
+          <t>東陽</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>7,990,000</t>
+          <t>27,850,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>4763</t>
+          <t>2211</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>材料*-KY</t>
+          <t>長榮鋼</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>41,500,000</t>
+          <t>20,540,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>4763</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>致伸</t>
+          <t>材料*-KY</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>29,006,000</t>
+          <t>41,500,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2211</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>長榮鋼</t>
+          <t>致伸</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>20,540,000</t>
+          <t>29,006,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
